--- a/artfynd/A 19133-2023 artfynd.xlsx
+++ b/artfynd/A 19133-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 19133-2023 artfynd.xlsx
+++ b/artfynd/A 19133-2023 artfynd.xlsx
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>108830832</v>
+        <v>108830716</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>876141.5134446596</v>
+        <v>876104</v>
       </c>
       <c r="R2" t="n">
-        <v>7380647.408774651</v>
+        <v>7380661</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,7 +746,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +756,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,49 +771,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sofia Sjöstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sofia Sjöstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>108833200</v>
+        <v>108830832</v>
       </c>
       <c r="B3" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>876273.7162911119</v>
+        <v>876141</v>
       </c>
       <c r="R3" t="n">
-        <v>7380807.210144123</v>
+        <v>7380648</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,7 +854,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +864,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,56 +879,47 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>108833021</v>
+        <v>108830869</v>
       </c>
       <c r="B4" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -946,13 +927,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>876218.0699666892</v>
+        <v>876131</v>
       </c>
       <c r="R4" t="n">
-        <v>7380833.415282276</v>
+        <v>7380654</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,7 +962,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +972,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,49 +987,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Alexander Nyberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Alexander Nyberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>108830716</v>
+        <v>108833200</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>876104.6531057162</v>
+        <v>876273</v>
       </c>
       <c r="R5" t="n">
-        <v>7380661.119276498</v>
+        <v>7380807</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1094,7 +1070,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1104,7 +1080,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,49 +1095,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sofia Sjöstrand</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sofia Sjöstrand</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>108830869</v>
+        <v>108833300</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1172,13 +1143,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>876130.3857319544</v>
+        <v>876265</v>
       </c>
       <c r="R6" t="n">
-        <v>7380654.43981505</v>
+        <v>7380812</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,44 +1203,39 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alexander Nyberg</t>
+          <t>Sofia Sjöstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexander Nyberg</t>
+          <t>Sofia Sjöstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>108833300</v>
+        <v>108833021</v>
       </c>
       <c r="B7" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1277,7 +1243,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1285,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>876264.6201207202</v>
+        <v>876218</v>
       </c>
       <c r="R7" t="n">
-        <v>7380811.262977324</v>
+        <v>7380834</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,12 +1315,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sofia Sjöstrand</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sofia Sjöstrand</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 19133-2023 artfynd.xlsx
+++ b/artfynd/A 19133-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108830716</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108830832</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108830869</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108833200</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108833300</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,8 +1354,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108833021</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>